--- a/docs/JMeter_全体パフォーマンステスト完全解説.xlsx
+++ b/docs/JMeter_全体パフォーマンステスト完全解説.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'06_全体観点'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_必要レポート'!$A$4:$F$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'07_必要レポート'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_実行注意点'!$A$4:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_実行注意点'!$A$4:$F$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'08_実行注意点'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_打ち込み位置'!$A$4:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'09_打ち込み位置'!$1:$3</definedName>
@@ -82,7 +82,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="22">'21_たとえ話集'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'22_コマンド集'!$A$4:$D$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="23">'22_コマンド集'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'23_参考情報'!$A$4:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'23_参考情報'!$A$4:$C$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="24">'23_参考情報'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,7 +636,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>小学生にも分かるたとえ話と、動作原理・歴史・最新仕様（2026-09）を一枚にまとめた実務ブック。詳細な文章は同梱の Markdown を、試験当日の表とチェックは本 Excel を使う。</t>
@@ -705,7 +705,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Java 8+ / 実行は Java 17 推奨</t>
+          <t>Java 8+ / 実行は Java 17 推奨。6.0 nightly は本試験に使わない</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>16KB 超 SQL は全エンジンでピン</t>
+          <t>16KB 超 SQL は全エンジンでピン。初期化クエリへ移してもアプリが SET を出すと残る</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ピン留め多数なら多重化が死んでいる</t>
+          <t>PostgreSQL にピン留めフィルタは無い</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>約束: 厨房の速さを知りたいのに校門の幅だけを測ってはいけない。測りたい部屋の直前からお客を入れる。</t>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>たとえ: 校門の警備員。厨房が速くても門が狭いと外では「学校が遅い」。2015年、API の認証・キー・レート制限の自作が限界になりマネージドの門が標準になった。</t>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>アカウント×リージョンの全 API 共有</t>
+          <t>HTTP/REST/WebSocket 合計。レートは申請可。バーストは顧客が指定できない</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10,000 RPS、バースト最大 5,000（一部リージョン 2,500/1,250）</t>
+          <t>多くは 10,000 RPS / バースト 5,000。一部は 2,500 / 1,250</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>HTTP / Lambda / VPC Link→ALB</t>
+          <t>HTTP / Lambda / VPC Link V2→ALB または NLB</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>IntegrationLatency が後ろの時間</t>
+          <t>IntegrationLatency が後ろの時間。認可は Latency との差の中</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>VPC Link v2 で private ALB 直結可</t>
+          <t>2025-11-21 以降 REST も private ALB 直結。V1 は NLB</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>帳票同期が 504。アプリは成功していることあり</t>
+          <t>延長は Regional/private のみ。スロットル引き下げがあり得る。アイドル接続は別で 310 秒</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>REST 29s（Regional/private は申請で延長可）、HTTP API 30s は不可</t>
+          <t>REST 29秒、HTTP API 30秒は不可。Lambda プロキシは 6MB</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>たとえ: 配膳口。2016年、コンテナとパスベースのために L7 特化で登場。Classic ELB の事前ウォーム文化は薄れたが、ゼロから数万 RPS を数秒では 503 があり得る。</t>
@@ -2364,22 +2364,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>HTTP client keepalive duration（2024〜、既定3600s）</t>
+          <t>client_keep_alive.seconds（2024-03〜、既定3600、範囲60〜604800）</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>接続の最大寿命</t>
+          <t>クライアントと ALB の最大寿命。ターゲット側ではない</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>長時間ソークでの再接続</t>
+          <t>期限後にもう1リクエストを受けて閉じる。ソークで Connect が周期的に跳ねる</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ジェネレータも追従</t>
+          <t>無効化不可。HTTP/2 PING は idle をリセットしない</t>
         </is>
       </c>
     </row>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>たとえ: 調理員ひとり。平均「普通」でも一人だけ炎上することがある。2014 ECS、2017 Fargate で課金と制限の単位がタスクサイズになった。2024-12 Container Insights enhanced。2026-06 に 20 秒メトリクスでスケール開始が大幅に短縮（公式ベンチ）。</t>
+          <t>たとえ: 調理員ひとり。平均「普通」でも一人だけ炎上することがある。2014 ECS、2017 Fargate で課金と制限の単位がタスクサイズになった。2024-12-02 Container Insights enhanced。2026-06-18 の 20 秒メトリクスは CPU/メモリのターゲット追跡のみでオプトイン。公式ベンチはトリガー 363秒→86秒。追加の CloudWatch 料金があり、有効化はデプロイを伴う。</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3095,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>高解像度 20s（2026〜）</t>
+          <t>高解像度 20s（2026-06-18〜、オプトイン）</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Service の CPU/メモリのみ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>速いスケール用</t>
+          <t>トリガー 363秒→86秒。用意まで 386秒→109秒</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>短いスパイクでも間に合わないことはある</t>
+          <t>既定ではない。RequestCountPerTarget は 20秒にならない。追加料金</t>
         </is>
       </c>
     </row>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v1（2018）は載せ替えで切れやすかった。v2（2022〜）は同じインスタンス内で ACU を細かく変える。ACU≒2GiB。min 0（ポーズ）〜 max 256。2026 年公式は 1 秒で +12 ACU などの高速化を発表。ゼロ遅延ではない。</t>
+          <t>v1（2018）は載せ替えで切れやすかった。v2（2022〜）は同じインスタンス内で ACU を細かく変える。ACU≒2GiB。対応版で min 0〜 max 256。2026-08-05 の発表は、プラットフォーム 3/4 で最初の1秒に最大12 ACUまで立ち上がり、その後256まで続く。毎秒 +12 ACU ではない。ポーズ復帰は約15秒。24時間超は30秒以上で、復帰後は小さい ACU から上がり直す。</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>暇なら畳む。復帰に時間がかかる（条件で十数秒）</t>
+          <t>接続があると畳まない。復帰は約15秒。24時間超は30秒以上。前の ACU には戻らない</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>本試験中は min&gt;0、事前ウォーム</t>
+          <t>本試験中は min&gt;0。接続タイムアウトは15秒より長く</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2019 年頃、Lambda/コンテナの接続嵐とフェイルオーバー切断を和らげるために登場。トランザクション単位で DB 接続を使い回す。セッション状態が付くとピン留め（1:1）。SQL 16KB 超は全エンジンでピン（公式）。</t>
+          <t>プレビューは 2019 年頃、一般提供は 2020 年。Lambda/コンテナの接続嵐とフェイルオーバー切断を和らげる。トランザクション単位で DB 接続を使い回す。SQL 16KB 超は全エンジンでピン。クライアント接続の最大寿命は 24 時間（変更不可）。IdleClientTimeout の既定は 30 分。MaxConnectionsPercent は直近ピークより少なくとも 30% 高くする。</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>idle を Proxy より短く。24h 寿命に注意</t>
+          <t>アプリの寿命は24時間未満。idle は IdleClientTimeout（既定30分）より短く</t>
         </is>
       </c>
     </row>
@@ -3634,17 +3634,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>公式ダッシュボードはピークの 30% 余裕を推奨</t>
+          <t>MaxConnectionsPercent は直近の最大使用量より少なくとも 30% 高くする（公式）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>MaxDatabaseConnectionsAllowed</t>
+          <t>MaxDatabaseConnectionsAllowed と DatabaseConnections</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>試験で 100% 埋めない</t>
+          <t>試験で許可枠を 100% 埋めない</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Initialization query へ寄せる</t>
+          <t>初期化クエリへ移し、アプリの SQL からも消す。PG はフィルタ不可</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>memcached 2003、Redis 2009、ElastiCache 2011、Valkey 選択肢 2024〜。接続確立（特に TLS）は GET より桁で高い。永続接続とプールが前提。</t>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>握手はコマンドより高い</t>
+          <t>握手はコマンドより高い。maxclients は多くの型で 65000、小さい t 系は 20000 や 46000</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CurrConnections、NewConnections</t>
+          <t>CurrConnections、NewConnections、ノード型の maxclients</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>日本の業務では見積・請求 PDF が同期 HTTP で残りやすい。SVF はジョブ並列・プリンタスレッド、Jasper はメモリと virtualizer。同期は API Gateway 29s / ALB idle / アプリ・JMeter タイムアウトの入れ子に当たる。</t>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Elapsed ≒ 往復 + (GW Latency-IntegrationLatency) + 認可 + ALB request + TargetResponseTime(アプリ+キャッシュ+Proxy+DB+帳票) + response。</t>
+          <t>Elapsed は入れ子。認可は (Latency-IntegrationLatency) の中なので別に足さない。ALB 直打ちに API Gateway の項は無い。Connect は Elapsed に含まれ、TargetResponseTime には入らない。</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>試験設計は 05〜09、当日オペは 20 チェックリスト、障害切り分けは 19 失敗の見分け。文章の深掘りは Markdown。</t>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>前提例: 内部 ALB、タスク 8、ACU ウォーム済み、帳票 5% 同期、ウォームアップ 10 分除外、定常 30 分。値は例。計画書の NFR に置き換える。</t>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>パスは環境で置き換える。Heap は set HEAP=-Xms4g -Xmx4g など。大きすぎる Xmx は GC 停止を長くする。</t>
@@ -8472,12 +8472,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>17 推奨</t>
+          <t>安定版 5.6.3 は Java 8 以上。実行は 17 推奨</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>8 未満は 5.6.3 不可</t>
+          <t>6.0 nightly は Java 17 必須。本試験に使わない</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>本ブックの数値は 2026-09 時点の公式ドキュメントに基づく。クォータ・ACU 上限・タイムアウトはアカウントとエンジン版で変わる。</t>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>APDEX、粒度 &gt;=1s</t>
+          <t>APDEX 既定500/1500。粒度は1000msより大きい。既定60000</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10k RPS、バースト、29s</t>
+          <t>多くは10k RPS/バースト5k。一部2500/1250。29秒延長でスロットル減があり得る</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ALB idle timeout</t>
+          <t>ALB idle と client keepalive</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>既定 60s、1-4000、keep-alive 整合</t>
+          <t>idle 既定60秒（1-4000）。client_keep_alive 既定3600（60-604800）</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>20s、2026-06</t>
+          <t>2026-06-18。オプトイン。トリガー363秒→86秒</t>
         </is>
       </c>
     </row>
@@ -8858,17 +8858,17 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Aurora 高速スケール（ブログ）</t>
+          <t>Aurora 初期スケール（2026-08-05）</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://aws.amazon.com/blogs/database/faster-scaling-for-aurora-serverless-to-support-agentic-ai-and-other-spiky-workloads/</t>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aurora-serverless-instant-12-acu-scaling/</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+12 ACU/s 等（発表値）</t>
+          <t>最初の1秒で最大12 ACU。プラットフォーム3/4。毎秒+12ではない</t>
         </is>
       </c>
     </row>
@@ -8902,80 +8902,63 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>24h、idle</t>
+          <t>寿命24時間。IdleClientTimeout 既定30分。MaxConnectionsPercent は直近ピーク+30%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>RDS Proxy ダッシュボード</t>
+          <t>SVF 並列・ログ</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://docs.aws.amazon.com/AmazonRDS/latest/UserGuide/rds-proxy-monitoring-dashboard.html</t>
+          <t>ウイングアーク KB（UCX 並列、一時ディレクトリ、デバッグ OFF）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>30% ヘッドルーム</t>
+          <t>帳票天井</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SVF 並列・ログ</t>
+          <t>JasperReports 負荷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ウイングアーク KB（UCX 並列、一時ディレクトリ、デバッグ OFF）</t>
+          <t>Jaspersoft Community（JMeter での負荷、virtualizer、同時実行）</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>帳票天井</t>
+          <t>メモリが先に限界になりやすい</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>JasperReports 負荷</t>
+          <t>同梱 Markdown</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Jaspersoft Community（JMeter での負荷、virtualizer、同時実行）</t>
+          <t>docs/JMeter_全体パフォーマンステスト完全解説.md</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>メモリが先に限界になりやすい</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>同梱 Markdown</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>docs/JMeter_全体パフォーマンステスト完全解説.md</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
           <t>文章の深掘り本体</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C24"/>
+  <autoFilter ref="A4:C23"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -9701,7 +9684,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019 preview / 2020-06 GA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -9760,12 +9743,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ALB keepalive 寿命、Aurora 高速スケール、ECS 20秒メトリクス</t>
+          <t>ALB client keepalive、Aurora 初期12 ACU、ECS 20秒メトリクス</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>突発負荷とエージェントワークロード</t>
+          <t>20秒と初期加速は既定の全環境には付かない</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -9797,7 +9780,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Coordinated Omission、非 GUI</t>
+          <t>Coordinated Omission はパーセンタイルでは直らない</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -9907,7 +9890,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>XML でツリーを保存。機能モードは本文保持でメモリ死</t>
+          <t>機能モードは本文を結果ファイルへ書く。CSV には効かない。Tree がメモリを食う</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -10062,12 +10045,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>電話をかけるまで</t>
+          <t>電話がつながるまで</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TCP/TLS 握手</t>
+          <t>TCP/TLS。Latency に含まれ、三つの時間は足さない</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -10094,12 +10077,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>相手が「はい」と言うまで</t>
+          <t>相手が最初に声を出すまで</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>最初のバイトまで（TTFB に近い）</t>
+          <t>送る直前から最初の応答まで。アップロードを含む。TTFB とは一致しない</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -10131,7 +10114,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>最後のバイトまで</t>
+          <t>送る直前から最後のバイトまで。Latency を含む</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -10163,12 +10146,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>親サンプルを TPS に出せる</t>
+          <t>合計サンプルは常に追加。親モードだと子は CSV に出ない</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>タイマーを含むかで SLA が変わる</t>
+          <t>既定オフ。統計の行を全部足すと二重</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10542,22 +10525,22 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>遅い時間に注文が減って平均が良く見える</t>
+          <t>出せなかった注文が記録されず、平均も p95 も良く見える</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>クローズドワークロードの性質</t>
+          <t>クローズドワークロードの性質。欠測は母集団に入らない</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>到着率モデルとパーセンタイル</t>
+          <t>到着率モデルと十分なスレッド</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>JMeter のバグ</t>
+          <t>パーセンタイルを見れば直る</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10722,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>認可・スロットル・統合。既定 10,000 RPS</t>
+          <t>多くは 10,000 RPS / バースト 5,000。一部は 2,500 / 1,250。バーストは申請不可</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -10803,17 +10786,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>REST 既定。HTTP API は30秒</t>
+          <t>REST 29秒。延長は Regional/private のみでスロットル引き下げがあり得る。HTTP API は30秒で不可</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>帳票同期の壁</t>
+          <t>帳票同期の壁。アイドル接続は別で310秒</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>アプリ設定で延びる</t>
+          <t>アプリ設定だけで延びる</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10818,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>L7 振り分け。idle 既定60s</t>
+          <t>idle 既定60秒（1-4000）。client keepalive は別で既定3600秒（クライアント側）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -10845,7 +10828,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Classic ELB と同じウォーム必須</t>
+          <t>keepalive 3600 をターゲットの寿命と同一視</t>
         </is>
       </c>
     </row>
@@ -11091,12 +11074,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>min=0。復帰に時間がかかる</t>
+          <t>min=0。復帰は約15秒。24時間超は30秒以上。復帰後は小さい ACU から</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>本試験中は禁止</t>
+          <t>本試験中は禁止。接続タイムアウトは15秒より長く</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -11155,17 +11138,17 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>SET・一時表・SQL&gt;16KB 等</t>
+          <t>SET・一時表・SQL&gt;16KB。PG にフィルタは無い</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Pinned メトリクス必須</t>
+          <t>Pinned メトリクス必須。SET はアプリからも外す</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>ログに必ず出るエラー</t>
+          <t>アプリが必ずエラーにする</t>
         </is>
       </c>
     </row>
@@ -12995,7 +12978,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>トランザクション親を含まない</t>
+          <t>Transaction Controller のサンプルは除く（公式）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13107,7 +13090,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>粒度 &lt;1s は公式非推奨</t>
+          <t>粒度は 1000ms より大きいこと。既定 60000。p95 は GUI と計算式が違う</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13284,7 +13267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13706,17 +13689,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>OOM</t>
+          <t>リソース増。CSV 自体は太らない</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>本文全保持</t>
+          <t>本文は結果ファイル向け。メモリ死の主因は Tree</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>OFF。本試験は CSV</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -13930,12 +13913,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>初回だけ十数秒</t>
+          <t>初回だけ約15秒。24時間超は30秒以上</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>コールドを SLA に</t>
+          <t>コールドを SLA に。復帰後は小さい ACU から</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -14085,22 +14068,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>HTML 粒度 &lt;1s</t>
+          <t>HTML 粒度が 1000ms 以下</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TPS グラフ崩壊</t>
+          <t>TPS グラフが不正</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>公式が警告</t>
+          <t>公式は 1 秒より大きいこと</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>&gt;=1000ms</t>
+          <t>既定 60000。1000 以下にしない</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -14109,8 +14092,232 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Generate parent sample をオン</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Hits/s が消える、または統計を足して二重</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>親モードでは子が CSV に出ない。オフでは子と合計の両方がある</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>既定のオフ。合計行を他と足さない</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard 14.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>REST 統合タイムアウトの延長</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>アカウント RPS が下がることがある</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>29秒超は Regional/private のみ。スロットル引き下げが条件になり得る</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>延長とクォータを同じ日付で記録</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Service Quotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ALB client keepalive 既定 3600秒</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ソークで約1時間ごとに Connect が跳ねる</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>クライアントと ALB の最大寿命。ターゲット側ではない</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>試験時間と比較。無効化不可</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>11_ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>ECS 20秒メトリクスが未設定</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>スケール開始が数分のまま</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>CPU/メモリのターゲット追跡だけ。追加料金。有効化はデプロイ</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>オプトインを別ランで確認</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>12_ECS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>setUp を sample_filter しない</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>準備リクエストが TPS に混ざる</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>JTL は全スレッドグループを残す</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>ラベルを分けて除外</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Header/Cookie Manager が複数</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>認証ヘッダが片方だけ</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Manager はマージされない。どれが使われるか指定できない</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>スコープに一つ</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>JMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Aurora を毎秒 +12 ACU と読む</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>伸縮の期待が過大</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 は最初の1秒で最大12 ACU。プラットフォーム 3/4</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>固定ランと伸縮ランを分ける</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>13_Aurora</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F28"/>
+  <autoFilter ref="A4:F35"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
